--- a/design/tables/TechnologyBranch.xlsx
+++ b/design/tables/TechnologyBranch.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyBranch" sheetId="1" r:id="Rabcb802b343d4e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyBranch" sheetId="1" r:id="R2694bc281b684009"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -289,6 +289,9 @@
       <x:c r="F1" s="3" t="str">
         <x:v>iconKey</x:v>
       </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>summaryKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -309,6 +312,9 @@
       <x:c r="F2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="G2" s="3" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -329,6 +335,9 @@
       <x:c r="F3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="3" t="str">
@@ -349,6 +358,9 @@
       <x:c r="F4" s="3" t="str">
         <x:v>iconKey</x:v>
       </x:c>
+      <x:c r="G4" s="3" t="str">
+        <x:v>summaryKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -369,6 +381,9 @@
       <x:c r="F5" s="3" t="str">
         <x:v>iconKey</x:v>
       </x:c>
+      <x:c r="G5" s="3" t="str">
+        <x:v>summaryKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
@@ -389,6 +404,9 @@
       <x:c r="F6" t="str">
         <x:v>menu:sprout</x:v>
       </x:c>
+      <x:c r="G6" t="str">
+        <x:v>tech.branch.sprout.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="n">
@@ -409,6 +427,9 @@
       <x:c r="F7" t="str">
         <x:v>menu:frost</x:v>
       </x:c>
+      <x:c r="G7" t="str">
+        <x:v>tech.branch.frost.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
@@ -429,6 +450,9 @@
       <x:c r="F8" t="str">
         <x:v>menu:bloom</x:v>
       </x:c>
+      <x:c r="G8" t="str">
+        <x:v>tech.branch.bloom.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
@@ -449,6 +473,9 @@
       <x:c r="F9" t="str">
         <x:v>menu:scope</x:v>
       </x:c>
+      <x:c r="G9" t="str">
+        <x:v>tech.branch.scope.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
@@ -469,6 +496,9 @@
       <x:c r="F10" t="str">
         <x:v>menu:spark</x:v>
       </x:c>
+      <x:c r="G10" t="str">
+        <x:v>tech.branch.spark.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
@@ -489,6 +519,9 @@
       <x:c r="F11" t="str">
         <x:v>menu:ember</x:v>
       </x:c>
+      <x:c r="G11" t="str">
+        <x:v>tech.branch.ember.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="n">
@@ -509,6 +542,9 @@
       <x:c r="F12" t="str">
         <x:v>menu:mint</x:v>
       </x:c>
+      <x:c r="G12" t="str">
+        <x:v>tech.branch.mint.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="n">
@@ -529,6 +565,9 @@
       <x:c r="F13" t="str">
         <x:v>menu:fan</x:v>
       </x:c>
+      <x:c r="G13" t="str">
+        <x:v>tech.branch.fan.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="n">
@@ -547,6 +586,9 @@
       <x:c r="F14" t="str">
         <x:v>ui:perk_E03</x:v>
       </x:c>
+      <x:c r="G14" t="str">
+        <x:v>tech.branch.logistics.summary</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="n">
@@ -564,6 +606,93 @@
       </x:c>
       <x:c r="F15" t="str">
         <x:v>ui:perk_X02</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>tech.branch.props.summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D16" t="str"/>
+      <x:c r="E16" t="str">
+        <x:v>tech.branch.boss</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>ui:tech_boss</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>tech.branch.boss.summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>clearing</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D17" t="str"/>
+      <x:c r="E17" t="str">
+        <x:v>tech.branch.clearing</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>ui:tech_clear</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>tech.branch.clearing.summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>salvage</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D18" t="str"/>
+      <x:c r="E18" t="str">
+        <x:v>tech.branch.salvage</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>ui:tech_recycle</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>tech.branch.salvage.summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>supply</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D19" t="str"/>
+      <x:c r="E19" t="str">
+        <x:v>tech.branch.supply</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>ui:tech_supply</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>tech.branch.supply.summary</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
